--- a/Result/profitability/3297.xlsx
+++ b/Result/profitability/3297.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,13 +669,13 @@
         <v>0.11</v>
       </c>
       <c r="M2" t="n">
-        <v>0.05</v>
+        <v>0.14</v>
       </c>
       <c r="N2" t="n">
-        <v>33.34625</v>
+        <v>33.835</v>
       </c>
       <c r="O2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>0.67</v>
       </c>
       <c r="M3" t="n">
-        <v>0.13125</v>
+        <v>0.2425</v>
       </c>
       <c r="N3" t="n">
-        <v>32.73625</v>
+        <v>33.10125</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -792,7 +792,7 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>0.65</v>
       </c>
       <c r="M4" t="n">
-        <v>0.23125</v>
+        <v>0.3325</v>
       </c>
       <c r="N4" t="n">
-        <v>31.98125</v>
+        <v>31.935</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>0.41</v>
       </c>
       <c r="M5" t="n">
-        <v>0.29125</v>
+        <v>0.34125</v>
       </c>
       <c r="N5" t="n">
-        <v>30.3375</v>
+        <v>30.47875</v>
       </c>
       <c r="O5" t="n">
         <v>1</v>
@@ -1137,10 +1137,10 @@
         <v>0.47</v>
       </c>
       <c r="M6" t="n">
-        <v>0.3075</v>
+        <v>0.36625</v>
       </c>
       <c r="N6" t="n">
-        <v>29.48875</v>
+        <v>29.39625</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1264,16 +1264,16 @@
         <v>0.34</v>
       </c>
       <c r="M7" t="n">
-        <v>0.31625</v>
+        <v>0.4175</v>
       </c>
       <c r="N7" t="n">
-        <v>27.995</v>
+        <v>28.70875</v>
       </c>
       <c r="O7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1282,7 +1282,7 @@
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="M8" t="n">
-        <v>0.41125</v>
+        <v>0.51</v>
       </c>
       <c r="N8" t="n">
-        <v>27.61625</v>
+        <v>27.5825</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1403,7 +1403,7 @@
         <v>1</v>
       </c>
       <c r="Q8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
@@ -1415,7 +1415,7 @@
         <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V8" t="n">
         <v>98.3</v>
@@ -1899,7 +1899,7 @@
         <v>0.48</v>
       </c>
       <c r="M12" t="n">
-        <v>0.5349999999999999</v>
+        <v>0.535</v>
       </c>
       <c r="N12" t="n">
         <v>26.68625</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>3297</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>65</v>
+      </c>
+      <c r="D75" t="n">
+        <v>42</v>
+      </c>
+      <c r="E75" t="n">
+        <v>24</v>
+      </c>
+      <c r="F75" t="n">
+        <v>36.41</v>
+      </c>
+      <c r="G75" t="n">
+        <v>-2</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>-2.30%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>28</v>
+      </c>
+      <c r="J75" t="n">
+        <v>27</v>
+      </c>
+      <c r="K75" t="n">
+        <v>27</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.12875</v>
+      </c>
+      <c r="N75" t="n">
+        <v>34.87375</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>1</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-15.8</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-0.2700000000000031</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.007360959651036114</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>1.176470588235294</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>1.129999999999995</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.03202947845804971</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
